--- a/metricas/rendimiento/rendimiento_resultados_y_plantilla.xlsx
+++ b/metricas/rendimiento/rendimiento_resultados_y_plantilla.xlsx
@@ -48,10 +48,10 @@
     <t xml:space="preserve">Pendiente: medición con el dashboard final (Power BI) y con datos reales del cliente.</t>
   </si>
   <si>
-    <t xml:space="preserve">Fecha y hora: 2026-10-27T15:38:45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Entorno: Chromium 153.0.8010.12 headless (Playwright) · Linux 6.18.44-fc-v165 · 2 CPU · contenedor en la nube, sin red externa (fuentes de Google no cargan)</t>
+    <t xml:space="preserve">Fecha y hora: 2026-10-27T20:12:40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entorno: Chromium 153.0.8010.12 headless (Playwright) · Linux 6.18.44-fc-v180 · 2 CPU · contenedor en la nube, sin red externa (fuentes de Google no cargan)</t>
   </si>
   <si>
     <t xml:space="preserve">Tamaño del dataset demo: 3.242 registros (2.528 con ventana completa); volumen: 50.000 registros remuestreados</t>
@@ -744,16 +744,16 @@
         <v>10</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>482.661496999981</v>
+        <v>448.271087000023</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>522.091296300005</v>
+        <v>473.521818700002</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>519.171965499993</v>
+        <v>465.255264500001</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>576.770815000032</v>
+        <v>504.045961000003</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>0</v>
@@ -778,16 +778,16 @@
         <v>10</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>79.3214130000024</v>
+        <v>70.3498979999893</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>93.9447476999931</v>
+        <v>89.6875860999984</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>93.4272709999959</v>
+        <v>83.9134054999988</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>122.921602000019</v>
+        <v>116.190466999996</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>0</v>
@@ -812,16 +812,16 @@
         <v>10</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>44.5711610000217</v>
+        <v>42.3232929999813</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>57.288889300014</v>
+        <v>54.758301199999</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>56.9365140000286</v>
+        <v>52.3901440000003</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>78.4744420000152</v>
+        <v>72.5217439999994</v>
       </c>
       <c r="H8" s="3" t="n">
         <v>0</v>
@@ -846,16 +846,16 @@
         <v>10</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>36.4828419999412</v>
+        <v>42.1790139999985</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>44.99112499999</v>
+        <v>51.5456661999991</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>46.2529705000065</v>
+        <v>47.4479439999982</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>52.2300919999452</v>
+        <v>65.0702910000121</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>0</v>
@@ -880,16 +880,16 @@
         <v>10</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>45.9638019999602</v>
+        <v>44.5292269999982</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>63.0464658000051</v>
+        <v>58.3129119000006</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>64.6559774999673</v>
+        <v>58.5311709999985</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>72.9804040000772</v>
+        <v>70.4681629999868</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>0</v>
@@ -914,16 +914,16 @@
         <v>20</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>16.9816560000982</v>
+        <v>13.3848709999995</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>24.763663300007</v>
+        <v>19.2722540500014</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>25.2187834999518</v>
+        <v>18.4335520000047</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>45.2699090000124</v>
+        <v>30.3928110000129</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>0</v>
@@ -950,16 +950,16 @@
         <v>20</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>35.8355309999752</v>
+        <v>33.0712370000015</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>53.4950870000046</v>
+        <v>40.9551043500031</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>56.1017160000006</v>
+        <v>40.1305000000036</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>64.8524610001005</v>
+        <v>49.9221150000153</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>0</v>
@@ -986,16 +986,16 @@
         <v>10</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>9.6</v>
+        <v>5.9</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>18.04</v>
+        <v>13.93</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>12.35</v>
+        <v>11.6</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>52.2</v>
+        <v>33.2</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>0</v>
@@ -1022,16 +1022,16 @@
         <v>1</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="H14" s="3" t="n">
         <v>0</v>
